--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-immunization#Immunization</t>
   </si>
   <si>
     <t>ID</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/immunization-basedOn</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/immunization-basedOn</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-immunization#Immunization</t>
+    <t>element:https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunization#Immunization</t>
   </si>
   <si>
     <t>ID</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-immunization-basedOn.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
